--- a/tool/kintone-resourse-generator/template/custom/K01_test.xlsx
+++ b/tool/kintone-resourse-generator/template/custom/K01_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\template\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79FE9F7-8F49-48FA-A72F-34FF9913C7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A4D395-1E44-4BA4-A0B0-E8D0F32E1298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>管理者</t>
   </si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>{PH}</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
   <si>
     <t>グループ</t>
@@ -150,9 +147,10 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -180,10 +178,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -499,21 +502,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.88671875" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="43.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -529,23 +533,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
+      <c r="C2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -558,15 +559,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.21875" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -580,47 +582,47 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="b">
+      <c r="C5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -633,24 +635,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -662,17 +665,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="17.77734375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -704,67 +706,67 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" t="b">
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -776,17 +778,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.77734375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -807,46 +810,6 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
